--- a/Modelo/datos/Intermedias/instance_template_v2.xlsx
+++ b/Modelo/datos/Intermedias/instance_template_v2.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21a7d57e8591b932/Escritorio/CICS/2025/Tesis/Objetivos de Aprendizaje/Modelo/datos/Intermedias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="8_{227CEB3E-0798-49E3-8725-EF741DAFAD66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95ACA04A-CF93-40E1-96AF-91856C7F5F20}"/>
+  <xr:revisionPtr revIDLastSave="205" documentId="8_{227CEB3E-0798-49E3-8725-EF741DAFAD66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C492E3B3-C6BC-46E0-92DA-9D534C198E9F}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="meta" sheetId="1" r:id="rId1"/>
-    <sheet name="concepts" sheetId="2" r:id="rId2"/>
-    <sheet name="precedence" sheetId="3" r:id="rId3"/>
+    <sheet name="README" sheetId="4" r:id="rId1"/>
+    <sheet name="meta" sheetId="1" r:id="rId2"/>
+    <sheet name="concepts" sheetId="2" r:id="rId3"/>
+    <sheet name="precedence" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>parameter</t>
   </si>
@@ -179,6 +180,15 @@
   </si>
   <si>
     <t>Comisiones_AFP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En hoja meta estan los parámetros originales del modelo, con el tiempo h dividido entre 10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En hoja concepts estan los 36 conceptos con su tiempo original a un 70% (entrevistas cognitivas) y dividido entre 10 y w que considera outdegree, decendentes y betwuennes (no recuerdo la proporción de cada uno) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En hoja precedence estan las precedencias considerando la matriz A completa (todos los enlaces) </t>
   </si>
 </sst>
 </file>
@@ -214,10 +224,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,6 +532,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDD9EC7A-A6EA-4CF0-AE0D-A99E342C4E75}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -576,9 +610,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -587,7 +621,7 @@
     <col min="4" max="4" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -601,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -609,13 +643,14 @@
         <v>12</v>
       </c>
       <c r="C2" s="1">
-        <v>70.728063636363629</v>
+        <v>7.0728063636363627</v>
       </c>
       <c r="D2">
         <v>6.9101564242838101E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -623,13 +658,14 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>101.30062727272725</v>
+        <v>10.130062727272726</v>
       </c>
       <c r="D3">
         <v>6.416053190562937E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -637,13 +673,14 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>55.332454545454532</v>
+        <v>5.5332454545454528</v>
       </c>
       <c r="D4">
         <v>6.7083803889782231E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
@@ -651,13 +688,14 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>53.15500909090909</v>
+        <v>5.3155009090909093</v>
       </c>
       <c r="D5">
         <v>5.1920501192771119E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
@@ -665,13 +703,14 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>35.106018181818179</v>
+        <v>3.5106018181818177</v>
       </c>
       <c r="D6">
         <v>4.5368365655809567E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
@@ -679,13 +718,14 @@
         <v>17</v>
       </c>
       <c r="C7">
-        <v>136.48495</v>
+        <v>13.648495</v>
       </c>
       <c r="D7">
         <v>4.2449637143848508E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
@@ -693,13 +733,14 @@
         <v>18</v>
       </c>
       <c r="C8">
-        <v>102.26311666666666</v>
+        <v>10.226311666666666</v>
       </c>
       <c r="D8">
         <v>4.8265890326189248E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
@@ -707,13 +748,14 @@
         <v>19</v>
       </c>
       <c r="C9">
-        <v>64.917416666666668</v>
+        <v>6.491741666666667</v>
       </c>
       <c r="D9">
         <v>5.6433483255081088E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
@@ -721,13 +763,14 @@
         <v>20</v>
       </c>
       <c r="C10">
-        <v>78.691549999999992</v>
+        <v>7.8691549999999992</v>
       </c>
       <c r="D10">
         <v>2.407737990182723E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
@@ -735,13 +778,14 @@
         <v>21</v>
       </c>
       <c r="C11">
-        <v>82.277416666666667</v>
+        <v>8.2277416666666667</v>
       </c>
       <c r="D11">
         <v>2.6312856684136379E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>11</v>
       </c>
@@ -749,13 +793,14 @@
         <v>22</v>
       </c>
       <c r="C12">
-        <v>102.28714999999998</v>
+        <v>10.228714999999998</v>
       </c>
       <c r="D12">
         <v>1.463150604217606E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>12</v>
       </c>
@@ -763,13 +808,14 @@
         <v>23</v>
       </c>
       <c r="C13">
-        <v>33.627766666666666</v>
+        <v>3.3627766666666665</v>
       </c>
       <c r="D13">
         <v>1.3188517869895999E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>13</v>
       </c>
@@ -777,13 +823,14 @@
         <v>24</v>
       </c>
       <c r="C14">
-        <v>59.263983333333321</v>
+        <v>5.9263983333333323</v>
       </c>
       <c r="D14">
         <v>1.2474407199292719E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -791,27 +838,29 @@
         <v>25</v>
       </c>
       <c r="C15">
-        <v>84.658583333333311</v>
+        <v>8.4658583333333315</v>
       </c>
       <c r="D15">
         <v>4.5348108219086142E-4</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="2">
-        <v>208.61761666666663</v>
+      <c r="C16">
+        <v>20.861761666666663</v>
       </c>
       <c r="D16">
         <v>9.4015733143731489E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>16</v>
       </c>
@@ -819,13 +868,14 @@
         <v>27</v>
       </c>
       <c r="C17">
-        <v>104.99241666666664</v>
+        <v>10.499241666666665</v>
       </c>
       <c r="D17">
         <v>6.4400777559451811E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>17</v>
       </c>
@@ -833,13 +883,14 @@
         <v>28</v>
       </c>
       <c r="C18">
-        <v>174.2552</v>
+        <v>17.425519999999999</v>
       </c>
       <c r="D18">
         <v>5.8759833539935288E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>18</v>
       </c>
@@ -847,13 +898,14 @@
         <v>29</v>
       </c>
       <c r="C19">
-        <v>55.669366666666669</v>
+        <v>5.5669366666666669</v>
       </c>
       <c r="D19">
         <v>4.5348108219086142E-4</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>19</v>
       </c>
@@ -861,13 +913,14 @@
         <v>30</v>
       </c>
       <c r="C20">
-        <v>74.611249999999984</v>
+        <v>7.4611249999999982</v>
       </c>
       <c r="D20">
         <v>5.1196356340826421E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>20</v>
       </c>
@@ -875,13 +928,14 @@
         <v>31</v>
       </c>
       <c r="C21">
-        <v>52.364783333333328</v>
+        <v>5.2364783333333325</v>
       </c>
       <c r="D21">
         <v>6.7997646068335658E-3</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>21</v>
       </c>
@@ -889,13 +943,14 @@
         <v>32</v>
       </c>
       <c r="C22">
-        <v>51.04796666666666</v>
+        <v>5.1047966666666662</v>
       </c>
       <c r="D22">
         <v>3.2905506781652659E-3</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>22</v>
       </c>
@@ -903,13 +958,14 @@
         <v>33</v>
       </c>
       <c r="C23">
-        <v>41.392633333333329</v>
+        <v>4.1392633333333331</v>
       </c>
       <c r="D23">
         <v>3.2905506781652659E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>23</v>
       </c>
@@ -917,13 +973,14 @@
         <v>34</v>
       </c>
       <c r="C24">
-        <v>47.002083333333324</v>
+        <v>4.7002083333333324</v>
       </c>
       <c r="D24">
         <v>4.5348108219086142E-4</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>24</v>
       </c>
@@ -931,28 +988,29 @@
         <v>35</v>
       </c>
       <c r="C25">
-        <v>61.960499999999989</v>
+        <v>6.1960499999999987</v>
       </c>
       <c r="D25">
         <v>2.8379839876550988E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="2">
-        <f t="shared" ref="C26:C27" si="0">C25*0.7</f>
-        <v>43.37234999999999</v>
+      <c r="C26">
+        <v>4.3372349999999988</v>
       </c>
       <c r="D26">
         <v>4.5348108219086142E-4</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>26</v>
       </c>
@@ -960,13 +1018,14 @@
         <v>37</v>
       </c>
       <c r="C27">
-        <v>70.985950000000003</v>
+        <v>7.0985950000000004</v>
       </c>
       <c r="D27">
         <v>2.3309313430266609E-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>27</v>
       </c>
@@ -974,13 +1033,14 @@
         <v>38</v>
       </c>
       <c r="C28">
-        <v>88.864066666666659</v>
+        <v>8.8864066666666659</v>
       </c>
       <c r="D28">
         <v>4.5348108219086142E-4</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>28</v>
       </c>
@@ -988,13 +1048,14 @@
         <v>39</v>
       </c>
       <c r="C29">
-        <v>95.23184999999998</v>
+        <v>9.523184999999998</v>
       </c>
       <c r="D29">
         <v>2.3309313430266609E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1002,13 +1063,14 @@
         <v>40</v>
       </c>
       <c r="C30">
-        <v>40.560566666666666</v>
+        <v>4.0560566666666666</v>
       </c>
       <c r="D30">
         <v>4.5348108219086142E-4</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1016,13 +1078,14 @@
         <v>41</v>
       </c>
       <c r="C31">
-        <v>66.072999999999993</v>
+        <v>6.6072999999999995</v>
       </c>
       <c r="D31">
         <v>4.8196221080933639E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1030,13 +1093,14 @@
         <v>42</v>
       </c>
       <c r="C32">
-        <v>76.454816666666659</v>
+        <v>7.6454816666666661</v>
       </c>
       <c r="D32">
         <v>5.4595008421495943E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1044,13 +1108,14 @@
         <v>43</v>
       </c>
       <c r="C33">
-        <v>54.727924999999999</v>
+        <v>5.4727924999999997</v>
       </c>
       <c r="D33">
         <v>4.5348108219086142E-4</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1058,13 +1123,14 @@
         <v>44</v>
       </c>
       <c r="C34">
-        <v>27.888063636363636</v>
+        <v>2.7888063636363638</v>
       </c>
       <c r="D34">
         <v>4.5348108219086142E-4</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1072,13 +1138,14 @@
         <v>45</v>
       </c>
       <c r="C35">
-        <v>33.558827272727264</v>
+        <v>3.3558827272727263</v>
       </c>
       <c r="D35">
         <v>4.5348108219086142E-4</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1086,13 +1153,14 @@
         <v>46</v>
       </c>
       <c r="C36">
-        <v>34.880745454545448</v>
+        <v>3.4880745454545448</v>
       </c>
       <c r="D36">
         <v>4.5348108219086142E-4</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1100,18 +1168,19 @@
         <v>47</v>
       </c>
       <c r="C37" s="1">
-        <v>21.265554545454542</v>
+        <v>2.1265554545454544</v>
       </c>
       <c r="D37">
         <v>4.5348108219086142E-4</v>
       </c>
+      <c r="E37" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
